--- a/changes/scar-stocks.xlsx
+++ b/changes/scar-stocks.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10802"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yifan\Documents\deadline-balancing\changes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yifan/Documents/deadline-balancing/changes/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364F2F4A-3AC9-4F9D-8F1C-394A5A4A0BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D04BA6-915D-7547-A021-D7642CDF9C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{605FF473-DEE6-48F8-84F5-1ADFC534E7D0}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="scar-stocks" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +33,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="49">
+  <si>
+    <t>new</t>
+  </si>
   <si>
     <t>name</t>
   </si>
@@ -59,9 +59,6 @@
     <t>magazine_capacity</t>
   </si>
   <si>
-    <t>bullet_deviation</t>
-  </si>
-  <si>
     <t>bullet_damage</t>
   </si>
   <si>
@@ -77,108 +74,102 @@
     <t>price</t>
   </si>
   <si>
-    <t>fn_scar_stock_connector</t>
-  </si>
-  <si>
-    <t>FN SCAR</t>
-  </si>
-  <si>
-    <t>fn_scar_ssr_stock_assembly</t>
-  </si>
-  <si>
-    <t>FN SCAR SSR</t>
-  </si>
-  <si>
-    <t>kinetic_development_group_sas_acr_stock_scar_adapter</t>
-  </si>
-  <si>
-    <t>Kinetic Development Group SAS Adaptive ACR Stock Connector</t>
+    <t>aft_stock_connector</t>
+  </si>
+  <si>
+    <t>AFT</t>
+  </si>
+  <si>
+    <t>aft_ssr_stock_assembly</t>
+  </si>
+  <si>
+    <t>AFT SSR</t>
+  </si>
+  <si>
+    <t>dynamic_development_group_sas_acr_stock_scar_adapter</t>
+  </si>
+  <si>
+    <t>Dynamic Development Group SAS Adaptive ACR</t>
   </si>
   <si>
     <t>mesa_tactical_faro_scar_buffer_tube_adapter</t>
   </si>
   <si>
-    <t>Mesa Tactical Faro Scar Buffer Tube Adapter</t>
-  </si>
-  <si>
-    <t>fn_scar_sc_stock_adapter</t>
-  </si>
-  <si>
-    <t>FN Scar SC Stock Adaptor</t>
-  </si>
-  <si>
-    <t>fn_scar_sc_stock_adjustment_lever</t>
-  </si>
-  <si>
-    <t>FN Scar SC Stock Adjustment Lever</t>
-  </si>
-  <si>
-    <t>fn_scar_sc_stock_cheekpad</t>
-  </si>
-  <si>
-    <t>FN Scar SC Stock Cheekpad</t>
-  </si>
-  <si>
-    <t>fn_scar_sc_stock_buttpad</t>
-  </si>
-  <si>
-    <t>FN Scar SC Stock Buttpad</t>
-  </si>
-  <si>
-    <t>fn_scar_sc_stock_adjustment_rail</t>
-  </si>
-  <si>
-    <t>FN Scar SC Stock Adjustment Rail</t>
-  </si>
-  <si>
-    <t>fn_scar_stock_shoulder_piece</t>
-  </si>
-  <si>
-    <t>fn_scar_stock_cheek_piece</t>
-  </si>
-  <si>
-    <t>kinetic_development_group_sas_acr_stock_cheek_pad</t>
-  </si>
-  <si>
-    <t>Kinetic Development Group SAS Adaptive ACR Stock</t>
-  </si>
-  <si>
-    <t>kinetic_development_group_sas_acr_stock</t>
+    <t>Canyon Tactical FARO FANG Buffer Tube</t>
+  </si>
+  <si>
+    <t>aft_sc_stock_adapter</t>
+  </si>
+  <si>
+    <t>AFT SC Rear</t>
+  </si>
+  <si>
+    <t>aft_stock_cheek_piece</t>
+  </si>
+  <si>
+    <t>aft_stock_shoulder_piece</t>
+  </si>
+  <si>
+    <t>dynamic_development_group_sas_acr_stock_retractor</t>
+  </si>
+  <si>
+    <t>Dynamic Development Group SAS Adaptive ACR Retractor</t>
+  </si>
+  <si>
+    <t>dynamic_development_group_sas_acr_stock_cheek_pad</t>
+  </si>
+  <si>
+    <t>Dynamic Development Group SAS Adaptive ACR Stock</t>
+  </si>
+  <si>
+    <t>dynamic_development_group_sas_acr_stock</t>
   </si>
   <si>
     <t>haga_defense_scar_acr_tailhook_adapter</t>
   </si>
   <si>
-    <t>Haga Defense SCAR ACR Tailhook</t>
-  </si>
-  <si>
-    <t>kinetic_development_group_sas_acr_stock_retractor</t>
-  </si>
-  <si>
-    <t>Kinetic Development Group SAS Adaptive ACR Retractor</t>
-  </si>
-  <si>
-    <t>ghw_tailhook_mod1_brace_small</t>
-  </si>
-  <si>
-    <t>GHW Tailhook MOD 1</t>
-  </si>
-  <si>
-    <t>ghw_tailhook_mod1_brace_big</t>
+    <t>Haga Defense FANG ACR Tailhook</t>
+  </si>
+  <si>
+    <t>gxw_tailhook_mod1_brace_small</t>
+  </si>
+  <si>
+    <t>GXW Tailhook MOD 1</t>
+  </si>
+  <si>
+    <t>gxw_tailhook_mod1_brace_big</t>
+  </si>
+  <si>
+    <t>aft_sc_stock_adjustment_lever</t>
+  </si>
+  <si>
+    <t>AFT SC Stock</t>
+  </si>
+  <si>
+    <t>aft_sc_stock_cheekpad</t>
+  </si>
+  <si>
+    <t>aft_sc_stock_buttpad</t>
+  </si>
+  <si>
+    <t>aft_sc_stock_adjustment_rail</t>
+  </si>
+  <si>
+    <t>AFT SC</t>
   </si>
   <si>
     <t>MOE Carbine</t>
   </si>
   <si>
+    <t>SCAR</t>
+  </si>
+  <si>
+    <t>SCAR SSR</t>
+  </si>
+  <si>
     <t>ACR</t>
   </si>
   <si>
-    <t>SCAR</t>
-  </si>
-  <si>
-    <t>SCAR SSR</t>
-  </si>
-  <si>
     <t>ACR brace</t>
   </si>
   <si>
@@ -188,7 +179,7 @@
     <t>buffer</t>
   </si>
   <si>
-    <t>new</t>
+    <t>barrel_deviation</t>
   </si>
 </sst>
 </file>
@@ -547,43 +538,43 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83DFBC53-4C18-48B7-B04F-4DA1626DC4B1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="46.85546875" customWidth="1"/>
-    <col min="2" max="2" width="49.140625" customWidth="1"/>
+    <col min="1" max="1" width="46.83203125" customWidth="1"/>
+    <col min="2" max="2" width="49.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="I2" t="s">
         <v>8</v>
@@ -601,7 +592,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>13</v>
       </c>
@@ -630,11 +621,11 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <f>C3-(D3*20)-(E3*0.8)-(F3*0.6)-(H3*5)</f>
+        <f t="shared" ref="N3:N32" si="0">C3-(D3*20)-(E3*0.8)-(F3*0.6)-(H3*5)</f>
         <v>-1.4000000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -642,19 +633,21 @@
         <v>16</v>
       </c>
       <c r="C4" s="1">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D4" s="1">
         <v>0.51</v>
       </c>
       <c r="E4" s="1">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="F4" s="1">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="H4" s="1">
+        <v>-0.05</v>
+      </c>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -663,11 +656,11 @@
         <v>600</v>
       </c>
       <c r="N4">
-        <f t="shared" ref="N4:N32" si="0">C4-(D4*20)-(E4*0.8)-(F4*0.6)-(H4*5)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+        <f t="shared" si="0"/>
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
@@ -700,7 +693,7 @@
         <v>-2.4000000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -708,21 +701,19 @@
         <v>20</v>
       </c>
       <c r="C6" s="1">
-        <v>-5</v>
+        <v>-4</v>
       </c>
       <c r="D6" s="1">
-        <v>0.08</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="E6" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1"/>
-      <c r="H6" s="1">
-        <v>0.1</v>
-      </c>
+      <c r="H6" s="1"/>
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
@@ -732,10 +723,10 @@
       </c>
       <c r="N6">
         <f t="shared" si="0"/>
-        <v>-9.8999999999999986</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+        <v>-6.8000000000000007</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>21</v>
       </c>
@@ -743,7 +734,7 @@
         <v>22</v>
       </c>
       <c r="C7" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="1">
         <v>0.08</v>
@@ -765,10 +756,10 @@
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
-        <v>-0.60000000000000009</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+        <v>-1.6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
@@ -787,9 +778,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B9" t="s">
         <v>14</v>
@@ -808,45 +799,45 @@
         <v>-0.20000000000000018</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
         <v>14</v>
       </c>
       <c r="C10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10">
         <v>0.19</v>
       </c>
       <c r="E10">
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="F10">
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="M10">
         <v>0</v>
       </c>
       <c r="N10">
         <f t="shared" si="0"/>
-        <v>17.600000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -862,12 +853,12 @@
         <v>-2.2000000000000002</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C13">
         <v>4</v>
@@ -883,45 +874,45 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14">
         <v>0.16</v>
       </c>
       <c r="E14">
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="F14">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="M14">
         <v>1000</v>
       </c>
       <c r="N14">
         <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+        <v>21.400000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N15">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -937,12 +928,12 @@
         <v>-1.2</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C17">
         <v>11</v>
@@ -951,25 +942,25 @@
         <v>0.09</v>
       </c>
       <c r="E17">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="F17">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="M17">
         <v>400</v>
       </c>
       <c r="N17">
         <f t="shared" si="0"/>
-        <v>16.2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C18">
         <v>11</v>
@@ -978,49 +969,49 @@
         <v>0.09</v>
       </c>
       <c r="E18">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="F18">
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="M18">
         <v>400</v>
       </c>
       <c r="N18">
         <f t="shared" si="0"/>
-        <v>16.2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+        <v>17.600000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N19">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C20">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20">
         <v>0.02</v>
       </c>
       <c r="N20">
         <f t="shared" si="0"/>
-        <v>1.6</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -1033,36 +1024,36 @@
         <v>3.2</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D22">
         <v>0.11</v>
       </c>
       <c r="E22">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="F22">
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="N22">
         <f t="shared" si="0"/>
-        <v>14.600000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C23">
         <v>0</v>
@@ -1075,79 +1066,79 @@
         <v>-1.6</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N24">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B25" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25">
+        <v>41</v>
+      </c>
+      <c r="C25" s="1">
         <v>17</v>
       </c>
-      <c r="D25">
-        <v>0.35</v>
-      </c>
-      <c r="E25">
+      <c r="D25" s="1">
+        <v>0.37</v>
+      </c>
+      <c r="E25" s="1">
         <v>-11</v>
       </c>
-      <c r="F25">
+      <c r="F25" s="1">
         <v>-10</v>
       </c>
-      <c r="G25">
-        <v>0</v>
-      </c>
-      <c r="H25">
-        <v>0</v>
-      </c>
-      <c r="I25">
-        <v>0</v>
-      </c>
-      <c r="J25">
-        <v>0</v>
-      </c>
-      <c r="K25">
-        <v>0</v>
-      </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
+      <c r="G25" s="1">
+        <v>0</v>
+      </c>
+      <c r="H25" s="1">
+        <v>0</v>
+      </c>
+      <c r="I25" s="1">
+        <v>0</v>
+      </c>
+      <c r="J25" s="1">
+        <v>0</v>
+      </c>
+      <c r="K25" s="1">
+        <v>0</v>
+      </c>
+      <c r="L25" s="1">
+        <v>0</v>
+      </c>
+      <c r="M25" s="1">
         <v>1400</v>
       </c>
       <c r="N25">
         <f t="shared" si="0"/>
-        <v>24.8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+        <v>24.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="N26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B27" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C27">
-        <f>C3+C9+C10</f>
-        <v>10</v>
+        <f t="shared" ref="C27:M27" si="1">C3+C9+C10</f>
+        <v>11</v>
       </c>
       <c r="D27">
-        <f t="shared" ref="D27:M27" si="1">D3+D9+D10</f>
+        <f t="shared" si="1"/>
         <v>0.42000000000000004</v>
       </c>
       <c r="E27">
         <f t="shared" si="1"/>
-        <v>-9</v>
+        <v>-10</v>
       </c>
       <c r="F27">
         <f t="shared" si="1"/>
-        <v>-12</v>
+        <v>-13</v>
       </c>
       <c r="G27">
         <f t="shared" si="1"/>
@@ -1179,28 +1170,28 @@
       </c>
       <c r="N27">
         <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+        <v>18.399999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C28">
-        <f>C4</f>
-        <v>20</v>
+        <f t="shared" ref="C28:M28" si="2">C4</f>
+        <v>18</v>
       </c>
       <c r="D28">
-        <f t="shared" ref="D28:M28" si="2">D4</f>
+        <f t="shared" si="2"/>
         <v>0.51</v>
       </c>
       <c r="E28">
         <f t="shared" si="2"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="F28">
         <f t="shared" si="2"/>
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="G28">
         <f t="shared" si="2"/>
@@ -1208,7 +1199,7 @@
       </c>
       <c r="H28">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="I28">
         <f t="shared" si="2"/>
@@ -1232,28 +1223,28 @@
       </c>
       <c r="N28">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+        <v>13.65</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B29" t="s">
         <v>44</v>
       </c>
       <c r="C29">
-        <f>C5+C12+C13+C14</f>
-        <v>13</v>
+        <f t="shared" ref="C29:M29" si="3">C5+C12+C13+C14</f>
+        <v>14</v>
       </c>
       <c r="D29">
-        <f t="shared" ref="D29:M29" si="3">D5+D12+D13+D14</f>
+        <f t="shared" si="3"/>
         <v>0.38</v>
       </c>
       <c r="E29">
         <f t="shared" si="3"/>
-        <v>-10</v>
+        <v>-11</v>
       </c>
       <c r="F29">
         <f t="shared" si="3"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G29">
         <f t="shared" si="3"/>
@@ -1285,28 +1276,28 @@
       </c>
       <c r="N29">
         <f t="shared" si="0"/>
-        <v>17.600000000000001</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C30">
-        <f>C5+C12+C13+C16+C17</f>
+        <f t="shared" ref="C30:M30" si="4">C5+C12+C13+C16+C17</f>
         <v>14</v>
       </c>
       <c r="D30">
-        <f t="shared" ref="D30:M30" si="4">D5+D12+D13+D16+D17</f>
+        <f t="shared" si="4"/>
         <v>0.37</v>
       </c>
       <c r="E30">
         <f t="shared" si="4"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="F30">
         <f t="shared" si="4"/>
-        <v>-5</v>
+        <v>-6</v>
       </c>
       <c r="G30">
         <f t="shared" si="4"/>
@@ -1338,28 +1329,28 @@
       </c>
       <c r="N30">
         <f t="shared" si="0"/>
-        <v>13.6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B31" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C31">
-        <f>C7+C20+C21+C22+C23</f>
-        <v>14</v>
+        <f t="shared" ref="C31:M31" si="5">C7+C20+C21+C22+C23</f>
+        <v>15</v>
       </c>
       <c r="D31">
-        <f t="shared" ref="D31:M31" si="5">D7+D20+D21+D22+D23</f>
+        <f t="shared" si="5"/>
         <v>0.33</v>
       </c>
       <c r="E31">
         <f t="shared" si="5"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="F31">
         <f t="shared" si="5"/>
-        <v>-7</v>
+        <v>-8</v>
       </c>
       <c r="G31">
         <f t="shared" si="5"/>
@@ -1391,28 +1382,28 @@
       </c>
       <c r="N31">
         <f t="shared" si="0"/>
-        <v>17.2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+        <v>19.599999999999998</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B32" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C32">
-        <f>C6+C25</f>
-        <v>12</v>
+        <f t="shared" ref="C32:M32" si="6">C6+C25</f>
+        <v>13</v>
       </c>
       <c r="D32">
-        <f t="shared" ref="D32:M32" si="6">D6+D25</f>
-        <v>0.43</v>
+        <f t="shared" si="6"/>
+        <v>0.51</v>
       </c>
       <c r="E32">
         <f t="shared" si="6"/>
-        <v>-9</v>
+        <v>-11</v>
       </c>
       <c r="F32">
         <f t="shared" si="6"/>
-        <v>-8</v>
+        <v>-10</v>
       </c>
       <c r="G32">
         <f t="shared" si="6"/>
@@ -1420,7 +1411,7 @@
       </c>
       <c r="H32">
         <f t="shared" si="6"/>
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I32">
         <f t="shared" si="6"/>
@@ -1444,10 +1435,11 @@
       </c>
       <c r="N32">
         <f t="shared" si="0"/>
-        <v>14.900000000000002</v>
+        <v>17.600000000000001</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>